--- a/SPM/SPM.xlsx
+++ b/SPM/SPM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM VII\Lab\SPM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E059A17-C2C7-428D-B578-AC5D507952F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D4179D-67C6-4C56-9447-A98C26170F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{0BB47063-B3A0-418A-AAA0-B73B74DF2503}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0BB47063-B3A0-418A-AAA0-B73B74DF2503}"/>
   </bookViews>
   <sheets>
     <sheet name="Lab1" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
   <si>
     <t>SN</t>
   </si>
@@ -129,9 +132,6 @@
   </si>
   <si>
     <t xml:space="preserve">PW of Cost: </t>
-  </si>
-  <si>
-    <t>&gt;1 Means Project is Acceptable</t>
   </si>
   <si>
     <t>Activity</t>
@@ -264,7 +264,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,25 +279,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -330,72 +336,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,383 +734,387 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE52EB5-E553-41E5-9C82-6B93D227FF19}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="78.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="13.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="78.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="16">
         <v>0</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="16">
         <v>-290000</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="16">
         <f>C2</f>
         <v>-290000</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="16">
         <f>1/(1+6/100)^B2</f>
         <v>1</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="16">
         <f>E2*C2</f>
         <v>-290000</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="16">
         <f>F2</f>
         <v>-290000</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="16">
         <v>1</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="16">
         <v>70000</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="16">
         <f>D2+C3</f>
         <v>-220000</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="17">
         <f t="shared" ref="E3:E7" si="0">1/(1+6/100)^B3</f>
         <v>0.94339622641509424</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="16">
         <f t="shared" ref="F3:F7" si="1">E3*C3</f>
         <v>66037.735849056597</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="16">
         <f>G2+F3</f>
         <v>-223962.2641509434</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="16">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="16">
         <v>70000</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="16">
         <f t="shared" ref="D4:D7" si="2">D3+C4</f>
         <v>-150000</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="17">
         <f t="shared" si="0"/>
         <v>0.88999644001423983</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="16">
         <f t="shared" si="1"/>
         <v>62299.750800996786</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="16">
         <f t="shared" ref="G4:G7" si="3">G3+F4</f>
         <v>-161662.51334994662</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="16">
         <v>3</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="16">
         <v>70000</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="16">
         <f t="shared" si="2"/>
         <v>-80000</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="17">
         <f t="shared" si="0"/>
         <v>0.8396192830323016</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="16">
         <f t="shared" si="1"/>
         <v>58773.349812261113</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="16">
         <f t="shared" si="3"/>
         <v>-102889.1635376855</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="16">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="16">
         <v>4</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="16">
         <v>70000</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="16">
         <f t="shared" si="2"/>
         <v>-10000</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="17">
         <f t="shared" si="0"/>
         <v>0.79209366323802044</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="16">
         <f t="shared" si="1"/>
         <v>55446.556426661431</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="16">
         <f t="shared" si="3"/>
         <v>-47442.607111024066</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="16">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="16">
         <v>5</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="16">
         <v>70000</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="16">
         <f t="shared" si="2"/>
         <v>60000</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="17">
         <f t="shared" si="0"/>
         <v>0.74725817286605689</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="16">
         <f t="shared" si="1"/>
         <v>52308.072100623984</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="16">
         <f t="shared" si="3"/>
         <v>4865.4649895999173</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="16">
         <f>COUNT(B3:B7)</f>
         <v>5</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="8">
+      <c r="C9" s="16">
         <f>SUM(C3:C7)</f>
         <v>350000</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="4" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="9">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="16">
         <f>ABS(C2)</f>
         <v>290000</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="20">
         <f>C9-C11</f>
         <v>60000</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="20" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="22">
         <f>(B14/ABS(C11))*100</f>
         <v>20.689655172413794</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="22">
         <f>(B14/B8)/ABS(C11)*100</f>
         <v>4.1379310344827589</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="22">
         <f>B6+(ABS(D6)/C7)</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="20">
         <f>SUM(F2:F7)</f>
         <v>4865.4649895999173</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="H18" s="19" t="s">
+      <c r="C18" s="20"/>
+      <c r="H18" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="24">
         <f>4+(ABS(G6)/F6)</f>
         <v>4.8556456914285722</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="25">
         <f>IRR(C2:C7,10)</f>
         <v>6.614607350584234E-2</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="H20" s="19" t="s">
+      <c r="C20" s="20"/>
+      <c r="H20" s="20" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="20">
         <f>SUM(F3:F7)</f>
         <v>294865.46498959995</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="H21" s="19" t="s">
+      <c r="C21" s="20"/>
+      <c r="H21" s="20" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="20">
         <f>F2</f>
         <v>-290000</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="H22" s="19" t="s">
+      <c r="C22" s="20"/>
+      <c r="H22" s="20" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="20">
         <f>B21/ABS(B22)</f>
         <v>1.016777465481379</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="1"/>
+      <c r="C23" s="21" t="str">
+        <f>IF(B23&gt;1,"&gt;1 means Project is Acceptable", "&lt;1 means Project is not Acceptable")</f>
+        <v>&gt;1 means Project is Acceptable</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1116,105 +1123,105 @@
   <dimension ref="B2:F10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="33.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.88671875" style="2"/>
-    <col min="5" max="5" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C3" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="20">
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="3">
         <v>300</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="3">
         <f>E3*D3</f>
         <v>600</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C4" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="20">
+      <c r="C4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="3">
         <v>3</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="3">
         <v>400</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="3">
         <f t="shared" ref="F4:F7" si="0">E4*D4</f>
         <v>1200</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C5" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="20">
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="3">
         <v>3</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="3">
         <v>400</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="3">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C6" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="20">
+      <c r="C6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="3">
         <v>200</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="3">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C7" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="20">
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="3">
         <v>100</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="3">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
-        <v>40</v>
+      <c r="B10" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1227,101 +1234,101 @@
   <dimension ref="B2:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.88671875" style="2"/>
-    <col min="4" max="4" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
+      <c r="E3" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="3">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="3">
+        <v>100</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="3">
+        <v>33</v>
+      </c>
+      <c r="E6" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="3">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3">
         <v>0</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="20">
-        <v>1</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="20">
-        <v>100</v>
-      </c>
-      <c r="E4" s="20">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="20">
-        <v>2</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="20">
-        <v>100</v>
-      </c>
-      <c r="E5" s="20">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="20">
-        <v>3</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="20">
-        <v>33</v>
-      </c>
-      <c r="E6" s="20">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="20">
-        <v>4</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="20">
-        <v>50</v>
-      </c>
-      <c r="E7" s="20">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="20">
-        <v>5</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="20">
-        <v>0</v>
-      </c>
-      <c r="E8" s="20">
+      <c r="E8" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1342,200 +1349,204 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2">
+      <c r="B2" s="8">
         <f>Lab3FieldReport!E4</f>
         <v>600</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <f>Lab3FieldReport!D4*'Lab3'!F3/100</f>
         <v>600</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="8">
         <v>100</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="8">
         <f>D2*'Lab3'!F3/100</f>
         <v>600</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="8">
         <f>Lab3FieldReport!E5</f>
         <v>1400</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <f>Lab3FieldReport!D5*'Lab3'!F4/100</f>
         <v>1200</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="8">
         <v>100</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="8">
         <f>D3*'Lab3'!F4/100</f>
         <v>1200</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4">
+      <c r="A4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="8">
         <f>Lab3FieldReport!E6</f>
         <v>500</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="8">
         <f>Lab3FieldReport!D6*'Lab3'!F5/100</f>
         <v>396</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="8">
         <v>66</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="8">
         <f>D4*'Lab3'!F5/100</f>
         <v>792</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5">
+      <c r="A5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="8">
         <f>Lab3FieldReport!E7</f>
         <v>200</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <f>Lab3FieldReport!D7*'Lab3'!F6/100</f>
         <v>200</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="8">
         <v>100</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="8">
         <f>D5*'Lab3'!F6/100</f>
         <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6">
+      <c r="A6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="8">
         <f>Lab3FieldReport!E8</f>
         <v>0</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <f>Lab3FieldReport!D8*'Lab3'!F7/100</f>
         <v>0</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="8">
         <v>0</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="8">
         <f>D6*'Lab3'!F7/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="9">
         <f>SUM(B2:B6)</f>
         <v>2700</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="9">
         <f>SUM(C2:C6)</f>
         <v>2396</v>
       </c>
-      <c r="E7">
+      <c r="D7" s="9"/>
+      <c r="E7" s="9">
         <f>SUM(E2:E6)</f>
         <v>2992</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="22">
+      <c r="B9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="11">
         <f>C7/B7</f>
         <v>0.88740740740740742</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="22">
+      <c r="B10" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="11">
         <f>C7/E7</f>
         <v>0.80080213903743314</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11">
+      <c r="B11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="12">
         <f>C7-B7</f>
         <v>-304</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12">
+      <c r="B12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="12">
         <f>C7-E7</f>
         <v>-596</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
+      <c r="C14" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D15" t="str">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13" t="str">
         <f>IF(D9&gt;1,"The Project is on Budget","The Project is Over Budget")</f>
         <v>The Project is Over Budget</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D16" t="str">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13" t="str">
         <f>IF(D10&gt;1,"The Project is on Schedule","The Project is Behind Schedule")</f>
         <v>The Project is Behind Schedule</v>
       </c>
